--- a/rulebook-examples/job-search-rag/xlsx/Job Search RAG.xlsx
+++ b/rulebook-examples/job-search-rag/xlsx/Job Search RAG.xlsx
@@ -2065,7 +2065,7 @@
     <t xml:space="preserve">{
   "$schema": "https://example.com/cmcc-schema/v1",
   "Name": "Job Search RAG",
-  "Description": "Rulebook for a local LLM + RAG pipeline that automates intelligent job filtering across multiple job boards using semantic search.",
+  "Description": "Local LLM + RAG pipeline filtering jobs across boards using semantic search.",
   "JobBoards": {
     "Description": "Table: JobBoards - Configured job board sources that can be crawled for listings.",
     "schema": [
@@ -2597,7 +2597,7 @@
         "Name": "Experience",
         "Resume": "resume-platform-2026q1",
         "SectionOrder": 3,
-        "Content": "## Experience\n### Staff Platform Engineer — CloudScale Inc (2022-2026)\nLed platform architecture for ML serving infrastructure. Designed multi-region Kubernetes deployment strategy. Reduced model inference latency 40%.\n### Senior Engineer — DataForge (2018-2022)\nBuilt real-time data pipelines processing 2M events/sec. Migrated monolith to event-driven microservices.",
+        "Content": "## Experience\n### Staff Platform Engineer \u2014 CloudScale Inc (2022-2026)\nLed platform architecture for ML serving infrastructure. Designed multi-region Kubernetes deployment strategy. Reduced model inference latency 40%.\n### Senior Engineer \u2014 DataForge (2018-2022)\nBuilt real-time data pipelines processing 2M events/sec. Migrated monolith to event-driven microservices.",
         "ChromaDocId": "resume-experience"
       },
       {
@@ -2605,7 +2605,7 @@
         "Name": "Earlier Roles",
         "Resume": "resume-platform-2026q1",
         "SectionOrder": 4,
-        "Content": "## Earlier Roles\n### Software Engineer — StartupCo (2014-2018)\nFull-stack development, API design, early DevOps adoption.\n### Junior Developer — Agency LLC (2011-2014)\nWeb application development, client projects, learned software engineering fundamentals.",
+        "Content": "## Earlier Roles\n### Software Engineer \u2014 StartupCo (2014-2018)\nFull-stack development, API design, early DevOps adoption.\n### Junior Developer \u2014 Agency LLC (2011-2014)\nWeb application development, client projects, learned software engineering fundamentals.",
         "ChromaDocId": "resume-earlier-roles"
       }
     ]
@@ -2927,10 +2927,10 @@
         "datatype": "number",
         "type": "raw",
         "nullable": false,
-        "Description": "Match to</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> role archetypes (0.0 - 1.0). Based on cosine distance in role_archetypes collection."
+        "Description": "Match to role archetypes (0.0 - 1.0). Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d on cosine distance in role_archetypes collection."
       },
       {
         "name": "HistoryScore",
